--- a/artfynd/A 49216-2025 artfynd.xlsx
+++ b/artfynd/A 49216-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129339074</v>
+        <v>129339067</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>91558</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>761628</v>
+        <v>761616</v>
       </c>
       <c r="R2" t="n">
-        <v>7227269</v>
+        <v>7227248</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129339067</v>
+        <v>129339074</v>
       </c>
       <c r="B3" t="n">
-        <v>91560</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>761616</v>
+        <v>761628</v>
       </c>
       <c r="R3" t="n">
-        <v>7227248</v>
+        <v>7227269</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129339076</v>
+        <v>129339066</v>
       </c>
       <c r="B9" t="n">
-        <v>79041</v>
+        <v>91558</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1379,21 +1379,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1403,10 +1403,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>761748</v>
+        <v>761609</v>
       </c>
       <c r="R9" t="n">
-        <v>7227187</v>
+        <v>7227328</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1465,10 +1465,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129339066</v>
+        <v>129339076</v>
       </c>
       <c r="B10" t="n">
-        <v>91560</v>
+        <v>79041</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1476,21 +1476,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>761609</v>
+        <v>761748</v>
       </c>
       <c r="R10" t="n">
-        <v>7227328</v>
+        <v>7227187</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1659,10 +1659,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129339060</v>
+        <v>129339075</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1670,42 +1670,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fågelmyran, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>761474</v>
+        <v>761753</v>
       </c>
       <c r="R12" t="n">
-        <v>7227325</v>
+        <v>7227209</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1738,11 +1730,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1769,10 +1756,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129339075</v>
+        <v>129339060</v>
       </c>
       <c r="B13" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1780,34 +1767,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Fågelmyran, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>761753</v>
+        <v>761474</v>
       </c>
       <c r="R13" t="n">
-        <v>7227209</v>
+        <v>7227325</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1840,6 +1835,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1866,32 +1866,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129339063</v>
+        <v>129339073</v>
       </c>
       <c r="B14" t="n">
-        <v>97555</v>
+        <v>79041</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1901,10 +1901,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>761450</v>
+        <v>761608</v>
       </c>
       <c r="R14" t="n">
-        <v>7227220</v>
+        <v>7227323</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1963,7 +1963,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129339073</v>
+        <v>129339070</v>
       </c>
       <c r="B15" t="n">
         <v>79041</v>
@@ -1998,10 +1998,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>761608</v>
+        <v>761468</v>
       </c>
       <c r="R15" t="n">
-        <v>7227323</v>
+        <v>7227315</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2060,32 +2060,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129339070</v>
+        <v>129339063</v>
       </c>
       <c r="B16" t="n">
-        <v>79041</v>
+        <v>97581</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2095,10 +2095,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>761468</v>
+        <v>761450</v>
       </c>
       <c r="R16" t="n">
-        <v>7227315</v>
+        <v>7227220</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2160,7 +2160,7 @@
         <v>129339078</v>
       </c>
       <c r="B17" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2254,10 +2254,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129339062</v>
+        <v>129339068</v>
       </c>
       <c r="B18" t="n">
-        <v>57887</v>
+        <v>79041</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2265,21 +2265,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>761581</v>
+        <v>761608</v>
       </c>
       <c r="R18" t="n">
-        <v>7227404</v>
+        <v>7227351</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2351,10 +2351,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129339068</v>
+        <v>129339062</v>
       </c>
       <c r="B19" t="n">
-        <v>79041</v>
+        <v>57887</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2362,21 +2362,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2386,10 +2386,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>761608</v>
+        <v>761581</v>
       </c>
       <c r="R19" t="n">
-        <v>7227351</v>
+        <v>7227404</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 49216-2025 artfynd.xlsx
+++ b/artfynd/A 49216-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129339067</v>
       </c>
       <c r="B2" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -695,14 +695,10 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -1368,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129339066</v>
+        <v>129339076</v>
       </c>
       <c r="B9" t="n">
-        <v>91558</v>
+        <v>79041</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1379,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1403,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>761609</v>
+        <v>761748</v>
       </c>
       <c r="R9" t="n">
-        <v>7227328</v>
+        <v>7227187</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1465,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129339076</v>
+        <v>129339066</v>
       </c>
       <c r="B10" t="n">
-        <v>79041</v>
+        <v>91560</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1476,23 +1472,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1500,10 +1492,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>761748</v>
+        <v>761609</v>
       </c>
       <c r="R10" t="n">
-        <v>7227187</v>
+        <v>7227328</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1562,27 +1554,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129339079</v>
+        <v>129339075</v>
       </c>
       <c r="B11" t="n">
-        <v>80181</v>
+        <v>79041</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1597,10 +1589,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>761435</v>
+        <v>761753</v>
       </c>
       <c r="R11" t="n">
-        <v>7227302</v>
+        <v>7227209</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1659,10 +1651,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129339075</v>
+        <v>129339060</v>
       </c>
       <c r="B12" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1670,34 +1662,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fågelmyran, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>761753</v>
+        <v>761474</v>
       </c>
       <c r="R12" t="n">
-        <v>7227209</v>
+        <v>7227325</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1730,6 +1730,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1756,53 +1761,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129339060</v>
+        <v>129339079</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>80181</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Fågelmyran, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>761474</v>
+        <v>761435</v>
       </c>
       <c r="R13" t="n">
-        <v>7227325</v>
+        <v>7227302</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1835,11 +1832,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1866,7 +1858,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129339073</v>
+        <v>129339070</v>
       </c>
       <c r="B14" t="n">
         <v>79041</v>
@@ -1901,10 +1893,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>761608</v>
+        <v>761468</v>
       </c>
       <c r="R14" t="n">
-        <v>7227323</v>
+        <v>7227315</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1963,7 +1955,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129339070</v>
+        <v>129339073</v>
       </c>
       <c r="B15" t="n">
         <v>79041</v>
@@ -1998,10 +1990,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>761468</v>
+        <v>761608</v>
       </c>
       <c r="R15" t="n">
-        <v>7227315</v>
+        <v>7227323</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2063,7 +2055,7 @@
         <v>129339063</v>
       </c>
       <c r="B16" t="n">
-        <v>97581</v>
+        <v>97582</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2160,7 +2152,7 @@
         <v>129339078</v>
       </c>
       <c r="B17" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 49216-2025 artfynd.xlsx
+++ b/artfynd/A 49216-2025 artfynd.xlsx
@@ -1554,10 +1554,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129339075</v>
+        <v>129339060</v>
       </c>
       <c r="B11" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1565,34 +1565,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fågelmyran, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>761753</v>
+        <v>761474</v>
       </c>
       <c r="R11" t="n">
-        <v>7227209</v>
+        <v>7227325</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1625,6 +1633,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1651,10 +1664,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129339060</v>
+        <v>129339075</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1662,42 +1675,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fågelmyran, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>761474</v>
+        <v>761753</v>
       </c>
       <c r="R12" t="n">
-        <v>7227325</v>
+        <v>7227209</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1730,11 +1735,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1858,7 +1858,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129339070</v>
+        <v>129339073</v>
       </c>
       <c r="B14" t="n">
         <v>79041</v>
@@ -1893,10 +1893,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>761468</v>
+        <v>761608</v>
       </c>
       <c r="R14" t="n">
-        <v>7227315</v>
+        <v>7227323</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1955,7 +1955,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129339073</v>
+        <v>129339070</v>
       </c>
       <c r="B15" t="n">
         <v>79041</v>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>761608</v>
+        <v>761468</v>
       </c>
       <c r="R15" t="n">
-        <v>7227323</v>
+        <v>7227315</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2055,7 +2055,7 @@
         <v>129339063</v>
       </c>
       <c r="B16" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 49216-2025 artfynd.xlsx
+++ b/artfynd/A 49216-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129339067</v>
+        <v>129339074</v>
       </c>
       <c r="B2" t="n">
-        <v>91560</v>
+        <v>79043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,19 +686,23 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -706,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>761616</v>
+        <v>761628</v>
       </c>
       <c r="R2" t="n">
-        <v>7227248</v>
+        <v>7227269</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -768,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129339074</v>
+        <v>129339067</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>91563</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -779,23 +783,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>761628</v>
+        <v>761616</v>
       </c>
       <c r="R3" t="n">
-        <v>7227269</v>
+        <v>7227248</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,7 +868,7 @@
         <v>129339069</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>129339077</v>
       </c>
       <c r="B5" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
         <v>129339065</v>
       </c>
       <c r="B6" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>129339072</v>
       </c>
       <c r="B7" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>129339076</v>
       </c>
       <c r="B9" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>129339066</v>
       </c>
       <c r="B10" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1554,53 +1554,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129339060</v>
+        <v>129339079</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>80183</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fågelmyran, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>761474</v>
+        <v>761435</v>
       </c>
       <c r="R11" t="n">
-        <v>7227325</v>
+        <v>7227302</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1633,11 +1625,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1664,10 +1651,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129339075</v>
+        <v>129339060</v>
       </c>
       <c r="B12" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1675,34 +1662,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fågelmyran, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>761753</v>
+        <v>761474</v>
       </c>
       <c r="R12" t="n">
-        <v>7227209</v>
+        <v>7227325</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1735,6 +1730,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1761,27 +1761,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129339079</v>
+        <v>129339075</v>
       </c>
       <c r="B13" t="n">
-        <v>80181</v>
+        <v>79043</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1796,10 +1796,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>761435</v>
+        <v>761753</v>
       </c>
       <c r="R13" t="n">
-        <v>7227302</v>
+        <v>7227209</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1861,7 +1861,7 @@
         <v>129339073</v>
       </c>
       <c r="B14" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>129339070</v>
       </c>
       <c r="B15" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>129339063</v>
       </c>
       <c r="B16" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>129339078</v>
       </c>
       <c r="B17" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2246,10 +2246,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129339068</v>
+        <v>129339062</v>
       </c>
       <c r="B18" t="n">
-        <v>79041</v>
+        <v>57887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2257,21 +2257,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2281,10 +2281,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>761608</v>
+        <v>761581</v>
       </c>
       <c r="R18" t="n">
-        <v>7227351</v>
+        <v>7227404</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2343,10 +2343,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129339062</v>
+        <v>129339068</v>
       </c>
       <c r="B19" t="n">
-        <v>57887</v>
+        <v>79043</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2354,21 +2354,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2378,10 +2378,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>761581</v>
+        <v>761608</v>
       </c>
       <c r="R19" t="n">
-        <v>7227404</v>
+        <v>7227351</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 49216-2025 artfynd.xlsx
+++ b/artfynd/A 49216-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129339074</v>
       </c>
       <c r="B2" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129339067</v>
+        <v>129339069</v>
       </c>
       <c r="B3" t="n">
-        <v>91563</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,19 +783,23 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -803,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>761616</v>
+        <v>761648</v>
       </c>
       <c r="R3" t="n">
-        <v>7227248</v>
+        <v>7227085</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129339069</v>
+        <v>129339067</v>
       </c>
       <c r="B4" t="n">
-        <v>79043</v>
+        <v>91565</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -876,23 +880,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>761648</v>
+        <v>761616</v>
       </c>
       <c r="R4" t="n">
-        <v>7227085</v>
+        <v>7227248</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,10 +962,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129339077</v>
+        <v>129339065</v>
       </c>
       <c r="B5" t="n">
-        <v>79043</v>
+        <v>80149</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -973,21 +973,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -997,10 +997,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>761517</v>
+        <v>761435</v>
       </c>
       <c r="R5" t="n">
-        <v>7227429</v>
+        <v>7227306</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1041,7 +1041,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1060,10 +1059,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129339065</v>
+        <v>129339077</v>
       </c>
       <c r="B6" t="n">
-        <v>80148</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1071,21 +1070,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1095,10 +1094,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>761435</v>
+        <v>761517</v>
       </c>
       <c r="R6" t="n">
-        <v>7227306</v>
+        <v>7227429</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1139,6 +1138,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1160,7 +1160,7 @@
         <v>129339072</v>
       </c>
       <c r="B7" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129339076</v>
+        <v>129339066</v>
       </c>
       <c r="B9" t="n">
-        <v>79043</v>
+        <v>91565</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,23 +1375,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1399,10 +1395,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>761748</v>
+        <v>761609</v>
       </c>
       <c r="R9" t="n">
-        <v>7227187</v>
+        <v>7227328</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1461,10 +1457,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129339066</v>
+        <v>129339076</v>
       </c>
       <c r="B10" t="n">
-        <v>91563</v>
+        <v>79044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,19 +1468,23 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>761609</v>
+        <v>761748</v>
       </c>
       <c r="R10" t="n">
-        <v>7227328</v>
+        <v>7227187</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1554,45 +1554,53 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129339079</v>
+        <v>129339060</v>
       </c>
       <c r="B11" t="n">
-        <v>80183</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fågelmyran, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>761435</v>
+        <v>761474</v>
       </c>
       <c r="R11" t="n">
-        <v>7227302</v>
+        <v>7227325</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1625,6 +1633,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1651,10 +1664,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129339060</v>
+        <v>129339075</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1662,42 +1675,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fågelmyran, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>761474</v>
+        <v>761753</v>
       </c>
       <c r="R12" t="n">
-        <v>7227325</v>
+        <v>7227209</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1730,11 +1735,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1761,27 +1761,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129339075</v>
+        <v>129339079</v>
       </c>
       <c r="B13" t="n">
-        <v>79043</v>
+        <v>80184</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1796,10 +1796,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>761753</v>
+        <v>761435</v>
       </c>
       <c r="R13" t="n">
-        <v>7227209</v>
+        <v>7227302</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1861,7 +1861,7 @@
         <v>129339073</v>
       </c>
       <c r="B14" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>129339070</v>
       </c>
       <c r="B15" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>129339063</v>
       </c>
       <c r="B16" t="n">
-        <v>97587</v>
+        <v>97589</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>129339078</v>
       </c>
       <c r="B17" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2246,10 +2246,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129339062</v>
+        <v>129339068</v>
       </c>
       <c r="B18" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2257,21 +2257,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2281,10 +2281,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>761581</v>
+        <v>761608</v>
       </c>
       <c r="R18" t="n">
-        <v>7227404</v>
+        <v>7227351</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2343,10 +2343,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129339068</v>
+        <v>129339062</v>
       </c>
       <c r="B19" t="n">
-        <v>79043</v>
+        <v>57887</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2354,21 +2354,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2378,10 +2378,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>761608</v>
+        <v>761581</v>
       </c>
       <c r="R19" t="n">
-        <v>7227351</v>
+        <v>7227404</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 49216-2025 artfynd.xlsx
+++ b/artfynd/A 49216-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129339074</v>
+        <v>129339067</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>91569</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,23 +686,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -710,10 +706,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>761628</v>
+        <v>761616</v>
       </c>
       <c r="R2" t="n">
-        <v>7227269</v>
+        <v>7227248</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +768,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129339069</v>
+        <v>129339074</v>
       </c>
       <c r="B3" t="n">
         <v>79044</v>
@@ -807,10 +803,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>761648</v>
+        <v>761628</v>
       </c>
       <c r="R3" t="n">
-        <v>7227085</v>
+        <v>7227269</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +865,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129339067</v>
+        <v>129339069</v>
       </c>
       <c r="B4" t="n">
-        <v>91565</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,19 +876,23 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>761616</v>
+        <v>761648</v>
       </c>
       <c r="R4" t="n">
-        <v>7227248</v>
+        <v>7227085</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1367,7 +1367,7 @@
         <v>129339066</v>
       </c>
       <c r="B9" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,10 +1554,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129339060</v>
+        <v>129339075</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1565,42 +1565,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fågelmyran, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>761474</v>
+        <v>761753</v>
       </c>
       <c r="R11" t="n">
-        <v>7227325</v>
+        <v>7227209</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1633,11 +1625,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1664,10 +1651,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129339075</v>
+        <v>129339060</v>
       </c>
       <c r="B12" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1675,34 +1662,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fågelmyran, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>761753</v>
+        <v>761474</v>
       </c>
       <c r="R12" t="n">
-        <v>7227209</v>
+        <v>7227325</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1735,6 +1730,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1858,32 +1858,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129339073</v>
+        <v>129339063</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>97593</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1893,10 +1893,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>761608</v>
+        <v>761450</v>
       </c>
       <c r="R14" t="n">
-        <v>7227323</v>
+        <v>7227220</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1955,7 +1955,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129339070</v>
+        <v>129339073</v>
       </c>
       <c r="B15" t="n">
         <v>79044</v>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>761468</v>
+        <v>761608</v>
       </c>
       <c r="R15" t="n">
-        <v>7227315</v>
+        <v>7227323</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2052,32 +2052,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129339063</v>
+        <v>129339070</v>
       </c>
       <c r="B16" t="n">
-        <v>97589</v>
+        <v>79044</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>761450</v>
+        <v>761468</v>
       </c>
       <c r="R16" t="n">
-        <v>7227220</v>
+        <v>7227315</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2152,7 +2152,7 @@
         <v>129339078</v>
       </c>
       <c r="B17" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 49216-2025 artfynd.xlsx
+++ b/artfynd/A 49216-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129339067</v>
+        <v>129339074</v>
       </c>
       <c r="B2" t="n">
-        <v>91569</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,19 +686,23 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -706,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>761616</v>
+        <v>761628</v>
       </c>
       <c r="R2" t="n">
-        <v>7227248</v>
+        <v>7227269</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -768,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129339074</v>
+        <v>129339069</v>
       </c>
       <c r="B3" t="n">
         <v>79044</v>
@@ -803,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>761628</v>
+        <v>761648</v>
       </c>
       <c r="R3" t="n">
-        <v>7227269</v>
+        <v>7227085</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129339069</v>
+        <v>129339067</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>91570</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -876,23 +880,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>761648</v>
+        <v>761616</v>
       </c>
       <c r="R4" t="n">
-        <v>7227085</v>
+        <v>7227248</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1367,7 +1367,7 @@
         <v>129339066</v>
       </c>
       <c r="B9" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,27 +1554,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129339075</v>
+        <v>129339079</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>80184</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>761753</v>
+        <v>761435</v>
       </c>
       <c r="R11" t="n">
-        <v>7227209</v>
+        <v>7227302</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1651,10 +1651,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129339060</v>
+        <v>129339075</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1662,42 +1662,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fågelmyran, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>761474</v>
+        <v>761753</v>
       </c>
       <c r="R12" t="n">
-        <v>7227325</v>
+        <v>7227209</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1730,11 +1722,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1761,45 +1748,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129339079</v>
+        <v>129339060</v>
       </c>
       <c r="B13" t="n">
-        <v>80184</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Fågelmyran, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>761435</v>
+        <v>761474</v>
       </c>
       <c r="R13" t="n">
-        <v>7227302</v>
+        <v>7227325</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1832,6 +1827,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1858,32 +1858,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129339063</v>
+        <v>129339073</v>
       </c>
       <c r="B14" t="n">
-        <v>97593</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1893,10 +1893,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>761450</v>
+        <v>761608</v>
       </c>
       <c r="R14" t="n">
-        <v>7227220</v>
+        <v>7227323</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1955,7 +1955,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129339073</v>
+        <v>129339070</v>
       </c>
       <c r="B15" t="n">
         <v>79044</v>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>761608</v>
+        <v>761468</v>
       </c>
       <c r="R15" t="n">
-        <v>7227323</v>
+        <v>7227315</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2052,32 +2052,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129339070</v>
+        <v>129339063</v>
       </c>
       <c r="B16" t="n">
-        <v>79044</v>
+        <v>97601</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>761468</v>
+        <v>761450</v>
       </c>
       <c r="R16" t="n">
-        <v>7227315</v>
+        <v>7227220</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2152,7 +2152,7 @@
         <v>129339078</v>
       </c>
       <c r="B17" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 49216-2025 artfynd.xlsx
+++ b/artfynd/A 49216-2025 artfynd.xlsx
@@ -962,10 +962,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129339065</v>
+        <v>129339077</v>
       </c>
       <c r="B5" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -973,21 +973,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -997,10 +997,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>761435</v>
+        <v>761517</v>
       </c>
       <c r="R5" t="n">
-        <v>7227306</v>
+        <v>7227429</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1041,6 +1041,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1059,10 +1060,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129339077</v>
+        <v>129339065</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1070,21 +1071,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1094,10 +1095,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>761517</v>
+        <v>761435</v>
       </c>
       <c r="R6" t="n">
-        <v>7227429</v>
+        <v>7227306</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1138,7 +1139,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129339066</v>
+        <v>129339076</v>
       </c>
       <c r="B9" t="n">
-        <v>91570</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,19 +1375,23 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1395,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>761609</v>
+        <v>761748</v>
       </c>
       <c r="R9" t="n">
-        <v>7227328</v>
+        <v>7227187</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1457,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129339076</v>
+        <v>129339066</v>
       </c>
       <c r="B10" t="n">
-        <v>79044</v>
+        <v>91570</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1468,23 +1472,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>761748</v>
+        <v>761609</v>
       </c>
       <c r="R10" t="n">
-        <v>7227187</v>
+        <v>7227328</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1554,27 +1554,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129339079</v>
+        <v>129339075</v>
       </c>
       <c r="B11" t="n">
-        <v>80184</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>761435</v>
+        <v>761753</v>
       </c>
       <c r="R11" t="n">
-        <v>7227302</v>
+        <v>7227209</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1651,27 +1651,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129339075</v>
+        <v>129339079</v>
       </c>
       <c r="B12" t="n">
-        <v>79044</v>
+        <v>80184</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>761753</v>
+        <v>761435</v>
       </c>
       <c r="R12" t="n">
-        <v>7227209</v>
+        <v>7227302</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1858,7 +1858,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129339073</v>
+        <v>129339070</v>
       </c>
       <c r="B14" t="n">
         <v>79044</v>
@@ -1893,10 +1893,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>761608</v>
+        <v>761468</v>
       </c>
       <c r="R14" t="n">
-        <v>7227323</v>
+        <v>7227315</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1955,7 +1955,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129339070</v>
+        <v>129339073</v>
       </c>
       <c r="B15" t="n">
         <v>79044</v>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>761468</v>
+        <v>761608</v>
       </c>
       <c r="R15" t="n">
-        <v>7227315</v>
+        <v>7227323</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2246,10 +2246,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129339068</v>
+        <v>129339062</v>
       </c>
       <c r="B18" t="n">
-        <v>79044</v>
+        <v>57887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2257,21 +2257,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2281,10 +2281,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>761608</v>
+        <v>761581</v>
       </c>
       <c r="R18" t="n">
-        <v>7227351</v>
+        <v>7227404</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2343,10 +2343,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129339062</v>
+        <v>129339068</v>
       </c>
       <c r="B19" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2354,21 +2354,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2378,10 +2378,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>761581</v>
+        <v>761608</v>
       </c>
       <c r="R19" t="n">
-        <v>7227404</v>
+        <v>7227351</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 49216-2025 artfynd.xlsx
+++ b/artfynd/A 49216-2025 artfynd.xlsx
@@ -1858,32 +1858,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129339070</v>
+        <v>129339063</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>97601</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1893,10 +1893,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>761468</v>
+        <v>761450</v>
       </c>
       <c r="R14" t="n">
-        <v>7227315</v>
+        <v>7227220</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1955,7 +1955,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129339073</v>
+        <v>129339070</v>
       </c>
       <c r="B15" t="n">
         <v>79044</v>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>761608</v>
+        <v>761468</v>
       </c>
       <c r="R15" t="n">
-        <v>7227323</v>
+        <v>7227315</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2052,32 +2052,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129339063</v>
+        <v>129339073</v>
       </c>
       <c r="B16" t="n">
-        <v>97601</v>
+        <v>79044</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>761450</v>
+        <v>761608</v>
       </c>
       <c r="R16" t="n">
-        <v>7227220</v>
+        <v>7227323</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 49216-2025 artfynd.xlsx
+++ b/artfynd/A 49216-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129339074</v>
+        <v>129339067</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>91573</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,23 +686,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -710,10 +706,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>761628</v>
+        <v>761616</v>
       </c>
       <c r="R2" t="n">
-        <v>7227269</v>
+        <v>7227248</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +768,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129339069</v>
+        <v>129339074</v>
       </c>
       <c r="B3" t="n">
         <v>79044</v>
@@ -807,10 +803,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>761648</v>
+        <v>761628</v>
       </c>
       <c r="R3" t="n">
-        <v>7227085</v>
+        <v>7227269</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +865,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129339067</v>
+        <v>129339069</v>
       </c>
       <c r="B4" t="n">
-        <v>91570</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,19 +876,23 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>761616</v>
+        <v>761648</v>
       </c>
       <c r="R4" t="n">
-        <v>7227248</v>
+        <v>7227085</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,10 +962,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129339077</v>
+        <v>129339065</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -973,21 +973,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -997,10 +997,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>761517</v>
+        <v>761435</v>
       </c>
       <c r="R5" t="n">
-        <v>7227429</v>
+        <v>7227306</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1041,7 +1041,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1060,10 +1059,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129339065</v>
+        <v>129339077</v>
       </c>
       <c r="B6" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1071,21 +1070,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1095,10 +1094,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>761435</v>
+        <v>761517</v>
       </c>
       <c r="R6" t="n">
-        <v>7227306</v>
+        <v>7227429</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1139,6 +1138,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129339076</v>
+        <v>129339066</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>91573</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,23 +1375,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1399,10 +1395,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>761748</v>
+        <v>761609</v>
       </c>
       <c r="R9" t="n">
-        <v>7227187</v>
+        <v>7227328</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1461,10 +1457,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129339066</v>
+        <v>129339076</v>
       </c>
       <c r="B10" t="n">
-        <v>91570</v>
+        <v>79044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,19 +1468,23 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>761609</v>
+        <v>761748</v>
       </c>
       <c r="R10" t="n">
-        <v>7227328</v>
+        <v>7227187</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1651,45 +1651,53 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129339079</v>
+        <v>129339060</v>
       </c>
       <c r="B12" t="n">
-        <v>80184</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fågelmyran, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>761435</v>
+        <v>761474</v>
       </c>
       <c r="R12" t="n">
-        <v>7227302</v>
+        <v>7227325</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1722,6 +1730,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1748,53 +1761,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129339060</v>
+        <v>129339079</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>80184</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Fågelmyran, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>761474</v>
+        <v>761435</v>
       </c>
       <c r="R13" t="n">
-        <v>7227325</v>
+        <v>7227302</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1827,11 +1832,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1858,32 +1858,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129339063</v>
+        <v>129339073</v>
       </c>
       <c r="B14" t="n">
-        <v>97601</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1893,10 +1893,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>761450</v>
+        <v>761608</v>
       </c>
       <c r="R14" t="n">
-        <v>7227220</v>
+        <v>7227323</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2052,32 +2052,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129339073</v>
+        <v>129339063</v>
       </c>
       <c r="B16" t="n">
-        <v>79044</v>
+        <v>97604</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>761608</v>
+        <v>761450</v>
       </c>
       <c r="R16" t="n">
-        <v>7227323</v>
+        <v>7227220</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2152,7 +2152,7 @@
         <v>129339078</v>
       </c>
       <c r="B17" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 49216-2025 artfynd.xlsx
+++ b/artfynd/A 49216-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129339067</v>
+        <v>129339074</v>
       </c>
       <c r="B2" t="n">
-        <v>91573</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,19 +686,23 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -706,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>761616</v>
+        <v>761628</v>
       </c>
       <c r="R2" t="n">
-        <v>7227248</v>
+        <v>7227269</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -768,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129339074</v>
+        <v>129339067</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>91573</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -779,23 +783,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>761628</v>
+        <v>761616</v>
       </c>
       <c r="R3" t="n">
-        <v>7227269</v>
+        <v>7227248</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -962,10 +962,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129339065</v>
+        <v>129339077</v>
       </c>
       <c r="B5" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -973,21 +973,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -997,10 +997,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>761435</v>
+        <v>761517</v>
       </c>
       <c r="R5" t="n">
-        <v>7227306</v>
+        <v>7227429</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1041,6 +1041,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1059,10 +1060,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129339077</v>
+        <v>129339065</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1070,21 +1071,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1094,10 +1095,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>761517</v>
+        <v>761435</v>
       </c>
       <c r="R6" t="n">
-        <v>7227429</v>
+        <v>7227306</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1138,7 +1139,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129339066</v>
+        <v>129339076</v>
       </c>
       <c r="B9" t="n">
-        <v>91573</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,19 +1375,23 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1395,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>761609</v>
+        <v>761748</v>
       </c>
       <c r="R9" t="n">
-        <v>7227328</v>
+        <v>7227187</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1457,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129339076</v>
+        <v>129339066</v>
       </c>
       <c r="B10" t="n">
-        <v>79044</v>
+        <v>91573</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1468,23 +1472,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>761748</v>
+        <v>761609</v>
       </c>
       <c r="R10" t="n">
-        <v>7227187</v>
+        <v>7227328</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1651,53 +1651,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129339060</v>
+        <v>129339079</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>80184</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fågelmyran, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>761474</v>
+        <v>761435</v>
       </c>
       <c r="R12" t="n">
-        <v>7227325</v>
+        <v>7227302</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1730,11 +1722,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1761,45 +1748,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129339079</v>
+        <v>129339060</v>
       </c>
       <c r="B13" t="n">
-        <v>80184</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Fågelmyran, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>761435</v>
+        <v>761474</v>
       </c>
       <c r="R13" t="n">
-        <v>7227302</v>
+        <v>7227325</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1832,6 +1827,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2246,10 +2246,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129339062</v>
+        <v>129339068</v>
       </c>
       <c r="B18" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2257,21 +2257,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2281,10 +2281,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>761581</v>
+        <v>761608</v>
       </c>
       <c r="R18" t="n">
-        <v>7227404</v>
+        <v>7227351</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2343,10 +2343,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129339068</v>
+        <v>129339062</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>57887</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2354,21 +2354,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2378,10 +2378,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>761608</v>
+        <v>761581</v>
       </c>
       <c r="R19" t="n">
-        <v>7227351</v>
+        <v>7227404</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 49216-2025 artfynd.xlsx
+++ b/artfynd/A 49216-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129339074</v>
+        <v>129339067</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>91573</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,23 +686,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -710,10 +706,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>761628</v>
+        <v>761616</v>
       </c>
       <c r="R2" t="n">
-        <v>7227269</v>
+        <v>7227248</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +768,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129339067</v>
+        <v>129339074</v>
       </c>
       <c r="B3" t="n">
-        <v>91573</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,19 +779,23 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>761616</v>
+        <v>761628</v>
       </c>
       <c r="R3" t="n">
-        <v>7227248</v>
+        <v>7227269</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -962,10 +962,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129339077</v>
+        <v>129339065</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -973,21 +973,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -997,10 +997,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>761517</v>
+        <v>761435</v>
       </c>
       <c r="R5" t="n">
-        <v>7227429</v>
+        <v>7227306</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1041,7 +1041,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1060,10 +1059,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129339065</v>
+        <v>129339077</v>
       </c>
       <c r="B6" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1071,21 +1070,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1095,10 +1094,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>761435</v>
+        <v>761517</v>
       </c>
       <c r="R6" t="n">
-        <v>7227306</v>
+        <v>7227429</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1139,6 +1138,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129339076</v>
+        <v>129339066</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>91573</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,23 +1375,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1399,10 +1395,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>761748</v>
+        <v>761609</v>
       </c>
       <c r="R9" t="n">
-        <v>7227187</v>
+        <v>7227328</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1461,10 +1457,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129339066</v>
+        <v>129339076</v>
       </c>
       <c r="B10" t="n">
-        <v>91573</v>
+        <v>79044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,19 +1468,23 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>761609</v>
+        <v>761748</v>
       </c>
       <c r="R10" t="n">
-        <v>7227328</v>
+        <v>7227187</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1554,27 +1554,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129339075</v>
+        <v>129339079</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>80184</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>761753</v>
+        <v>761435</v>
       </c>
       <c r="R11" t="n">
-        <v>7227209</v>
+        <v>7227302</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1651,27 +1651,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129339079</v>
+        <v>129339075</v>
       </c>
       <c r="B12" t="n">
-        <v>80184</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>761435</v>
+        <v>761753</v>
       </c>
       <c r="R12" t="n">
-        <v>7227302</v>
+        <v>7227209</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1858,32 +1858,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129339073</v>
+        <v>129339063</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>97604</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1893,10 +1893,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>761608</v>
+        <v>761450</v>
       </c>
       <c r="R14" t="n">
-        <v>7227323</v>
+        <v>7227220</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2052,32 +2052,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129339063</v>
+        <v>129339073</v>
       </c>
       <c r="B16" t="n">
-        <v>97604</v>
+        <v>79044</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>761450</v>
+        <v>761608</v>
       </c>
       <c r="R16" t="n">
-        <v>7227220</v>
+        <v>7227323</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 49216-2025 artfynd.xlsx
+++ b/artfynd/A 49216-2025 artfynd.xlsx
@@ -962,10 +962,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129339065</v>
+        <v>129339077</v>
       </c>
       <c r="B5" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -973,21 +973,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -997,10 +997,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>761435</v>
+        <v>761517</v>
       </c>
       <c r="R5" t="n">
-        <v>7227306</v>
+        <v>7227429</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1041,6 +1041,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1059,10 +1060,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129339077</v>
+        <v>129339065</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1070,21 +1071,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1094,10 +1095,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>761517</v>
+        <v>761435</v>
       </c>
       <c r="R6" t="n">
-        <v>7227429</v>
+        <v>7227306</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1138,7 +1139,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129339066</v>
+        <v>129339076</v>
       </c>
       <c r="B9" t="n">
-        <v>91573</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,19 +1375,23 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1395,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>761609</v>
+        <v>761748</v>
       </c>
       <c r="R9" t="n">
-        <v>7227328</v>
+        <v>7227187</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1457,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129339076</v>
+        <v>129339066</v>
       </c>
       <c r="B10" t="n">
-        <v>79044</v>
+        <v>91573</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1468,23 +1472,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>761748</v>
+        <v>761609</v>
       </c>
       <c r="R10" t="n">
-        <v>7227187</v>
+        <v>7227328</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1554,27 +1554,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129339079</v>
+        <v>129339075</v>
       </c>
       <c r="B11" t="n">
-        <v>80184</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>761435</v>
+        <v>761753</v>
       </c>
       <c r="R11" t="n">
-        <v>7227302</v>
+        <v>7227209</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1651,10 +1651,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129339075</v>
+        <v>129339060</v>
       </c>
       <c r="B12" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1662,34 +1662,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fågelmyran, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>761753</v>
+        <v>761474</v>
       </c>
       <c r="R12" t="n">
-        <v>7227209</v>
+        <v>7227325</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1722,6 +1730,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1748,53 +1761,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129339060</v>
+        <v>129339079</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>80184</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Fågelmyran, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>761474</v>
+        <v>761435</v>
       </c>
       <c r="R13" t="n">
-        <v>7227325</v>
+        <v>7227302</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1827,11 +1832,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1858,32 +1858,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129339063</v>
+        <v>129339073</v>
       </c>
       <c r="B14" t="n">
-        <v>97604</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1893,10 +1893,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>761450</v>
+        <v>761608</v>
       </c>
       <c r="R14" t="n">
-        <v>7227220</v>
+        <v>7227323</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2052,32 +2052,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129339073</v>
+        <v>129339063</v>
       </c>
       <c r="B16" t="n">
-        <v>79044</v>
+        <v>97604</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>761608</v>
+        <v>761450</v>
       </c>
       <c r="R16" t="n">
-        <v>7227323</v>
+        <v>7227220</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2246,10 +2246,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129339068</v>
+        <v>129339062</v>
       </c>
       <c r="B18" t="n">
-        <v>79044</v>
+        <v>57887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2257,21 +2257,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2281,10 +2281,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>761608</v>
+        <v>761581</v>
       </c>
       <c r="R18" t="n">
-        <v>7227351</v>
+        <v>7227404</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2343,10 +2343,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129339062</v>
+        <v>129339068</v>
       </c>
       <c r="B19" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2354,21 +2354,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2378,10 +2378,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>761581</v>
+        <v>761608</v>
       </c>
       <c r="R19" t="n">
-        <v>7227404</v>
+        <v>7227351</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 49216-2025 artfynd.xlsx
+++ b/artfynd/A 49216-2025 artfynd.xlsx
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129339076</v>
+        <v>129339066</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>91573</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,23 +1375,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1399,10 +1395,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>761748</v>
+        <v>761609</v>
       </c>
       <c r="R9" t="n">
-        <v>7227187</v>
+        <v>7227328</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1461,10 +1457,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129339066</v>
+        <v>129339076</v>
       </c>
       <c r="B10" t="n">
-        <v>91573</v>
+        <v>79044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,19 +1468,23 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>761609</v>
+        <v>761748</v>
       </c>
       <c r="R10" t="n">
-        <v>7227328</v>
+        <v>7227187</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1651,53 +1651,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129339060</v>
+        <v>129339079</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>80184</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fågelmyran, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>761474</v>
+        <v>761435</v>
       </c>
       <c r="R12" t="n">
-        <v>7227325</v>
+        <v>7227302</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1730,11 +1722,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1761,45 +1748,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129339079</v>
+        <v>129339060</v>
       </c>
       <c r="B13" t="n">
-        <v>80184</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Fågelmyran, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>761435</v>
+        <v>761474</v>
       </c>
       <c r="R13" t="n">
-        <v>7227302</v>
+        <v>7227325</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1832,6 +1827,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1858,7 +1858,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129339073</v>
+        <v>129339070</v>
       </c>
       <c r="B14" t="n">
         <v>79044</v>
@@ -1893,10 +1893,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>761608</v>
+        <v>761468</v>
       </c>
       <c r="R14" t="n">
-        <v>7227323</v>
+        <v>7227315</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1955,7 +1955,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129339070</v>
+        <v>129339073</v>
       </c>
       <c r="B15" t="n">
         <v>79044</v>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>761468</v>
+        <v>761608</v>
       </c>
       <c r="R15" t="n">
-        <v>7227315</v>
+        <v>7227323</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2246,10 +2246,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129339062</v>
+        <v>129339068</v>
       </c>
       <c r="B18" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2257,21 +2257,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2281,10 +2281,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>761581</v>
+        <v>761608</v>
       </c>
       <c r="R18" t="n">
-        <v>7227404</v>
+        <v>7227351</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2343,10 +2343,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129339068</v>
+        <v>129339062</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>57887</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2354,21 +2354,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2378,10 +2378,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>761608</v>
+        <v>761581</v>
       </c>
       <c r="R19" t="n">
-        <v>7227351</v>
+        <v>7227404</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 49216-2025 artfynd.xlsx
+++ b/artfynd/A 49216-2025 artfynd.xlsx
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129339066</v>
+        <v>129339076</v>
       </c>
       <c r="B9" t="n">
-        <v>91573</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,19 +1375,23 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1395,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>761609</v>
+        <v>761748</v>
       </c>
       <c r="R9" t="n">
-        <v>7227328</v>
+        <v>7227187</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1457,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129339076</v>
+        <v>129339066</v>
       </c>
       <c r="B10" t="n">
-        <v>79044</v>
+        <v>91573</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1468,23 +1472,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>761748</v>
+        <v>761609</v>
       </c>
       <c r="R10" t="n">
-        <v>7227187</v>
+        <v>7227328</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1554,10 +1554,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129339075</v>
+        <v>129339060</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1565,34 +1565,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fågelmyran, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>761753</v>
+        <v>761474</v>
       </c>
       <c r="R11" t="n">
-        <v>7227209</v>
+        <v>7227325</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1625,6 +1633,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1748,10 +1761,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129339060</v>
+        <v>129339075</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1759,42 +1772,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Fågelmyran, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>761474</v>
+        <v>761753</v>
       </c>
       <c r="R13" t="n">
-        <v>7227325</v>
+        <v>7227209</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1827,11 +1832,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1858,7 +1858,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129339070</v>
+        <v>129339073</v>
       </c>
       <c r="B14" t="n">
         <v>79044</v>
@@ -1893,10 +1893,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>761468</v>
+        <v>761608</v>
       </c>
       <c r="R14" t="n">
-        <v>7227315</v>
+        <v>7227323</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1955,7 +1955,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129339073</v>
+        <v>129339070</v>
       </c>
       <c r="B15" t="n">
         <v>79044</v>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>761608</v>
+        <v>761468</v>
       </c>
       <c r="R15" t="n">
-        <v>7227323</v>
+        <v>7227315</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 49216-2025 artfynd.xlsx
+++ b/artfynd/A 49216-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129339067</v>
+        <v>129339074</v>
       </c>
       <c r="B2" t="n">
-        <v>91573</v>
+        <v>79070</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,19 +686,23 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -706,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>761616</v>
+        <v>761628</v>
       </c>
       <c r="R2" t="n">
-        <v>7227248</v>
+        <v>7227269</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -768,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129339074</v>
+        <v>129339069</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>761628</v>
+        <v>761648</v>
       </c>
       <c r="R3" t="n">
-        <v>7227269</v>
+        <v>7227085</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129339069</v>
+        <v>129339067</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>91601</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -876,23 +880,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>761648</v>
+        <v>761616</v>
       </c>
       <c r="R4" t="n">
-        <v>7227085</v>
+        <v>7227248</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,7 +965,7 @@
         <v>129339077</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
         <v>129339065</v>
       </c>
       <c r="B6" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>129339072</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>129339061</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>129339076</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>129339066</v>
       </c>
       <c r="B10" t="n">
-        <v>91573</v>
+        <v>91601</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1554,10 +1554,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129339060</v>
+        <v>129339075</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>79070</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1565,42 +1565,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fågelmyran, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>761474</v>
+        <v>761753</v>
       </c>
       <c r="R11" t="n">
-        <v>7227325</v>
+        <v>7227209</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1633,11 +1625,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1664,45 +1651,53 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129339079</v>
+        <v>129339060</v>
       </c>
       <c r="B12" t="n">
-        <v>80184</v>
+        <v>57730</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fågelmyran, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>761435</v>
+        <v>761474</v>
       </c>
       <c r="R12" t="n">
-        <v>7227302</v>
+        <v>7227325</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1735,6 +1730,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1761,27 +1761,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129339075</v>
+        <v>129339079</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>80210</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1796,10 +1796,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>761753</v>
+        <v>761435</v>
       </c>
       <c r="R13" t="n">
-        <v>7227209</v>
+        <v>7227302</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1861,7 +1861,7 @@
         <v>129339073</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>129339070</v>
       </c>
       <c r="B15" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>129339063</v>
       </c>
       <c r="B16" t="n">
-        <v>97604</v>
+        <v>97633</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>129339078</v>
       </c>
       <c r="B17" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2246,10 +2246,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129339068</v>
+        <v>129339062</v>
       </c>
       <c r="B18" t="n">
-        <v>79044</v>
+        <v>57890</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2257,21 +2257,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2281,10 +2281,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>761608</v>
+        <v>761581</v>
       </c>
       <c r="R18" t="n">
-        <v>7227351</v>
+        <v>7227404</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2343,10 +2343,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129339062</v>
+        <v>129339068</v>
       </c>
       <c r="B19" t="n">
-        <v>57887</v>
+        <v>79070</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2354,21 +2354,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2378,10 +2378,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>761581</v>
+        <v>761608</v>
       </c>
       <c r="R19" t="n">
-        <v>7227404</v>
+        <v>7227351</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 49216-2025 artfynd.xlsx
+++ b/artfynd/A 49216-2025 artfynd.xlsx
@@ -962,10 +962,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129339077</v>
+        <v>129339065</v>
       </c>
       <c r="B5" t="n">
-        <v>79070</v>
+        <v>80175</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -973,21 +973,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -997,10 +997,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>761517</v>
+        <v>761435</v>
       </c>
       <c r="R5" t="n">
-        <v>7227429</v>
+        <v>7227306</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1041,7 +1041,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1060,10 +1059,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129339065</v>
+        <v>129339077</v>
       </c>
       <c r="B6" t="n">
-        <v>80175</v>
+        <v>79070</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1071,21 +1070,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1095,10 +1094,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>761435</v>
+        <v>761517</v>
       </c>
       <c r="R6" t="n">
-        <v>7227306</v>
+        <v>7227429</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1139,6 +1138,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1554,27 +1554,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129339075</v>
+        <v>129339079</v>
       </c>
       <c r="B11" t="n">
-        <v>79070</v>
+        <v>80210</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>761753</v>
+        <v>761435</v>
       </c>
       <c r="R11" t="n">
-        <v>7227209</v>
+        <v>7227302</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1651,10 +1651,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129339060</v>
+        <v>129339075</v>
       </c>
       <c r="B12" t="n">
-        <v>57730</v>
+        <v>79070</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1662,42 +1662,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fågelmyran, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>761474</v>
+        <v>761753</v>
       </c>
       <c r="R12" t="n">
-        <v>7227325</v>
+        <v>7227209</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1730,11 +1722,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1761,45 +1748,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129339079</v>
+        <v>129339060</v>
       </c>
       <c r="B13" t="n">
-        <v>80210</v>
+        <v>57730</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Fågelmyran, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>761435</v>
+        <v>761474</v>
       </c>
       <c r="R13" t="n">
-        <v>7227302</v>
+        <v>7227325</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1832,6 +1827,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1858,32 +1858,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129339073</v>
+        <v>129339063</v>
       </c>
       <c r="B14" t="n">
-        <v>79070</v>
+        <v>97633</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1893,10 +1893,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>761608</v>
+        <v>761450</v>
       </c>
       <c r="R14" t="n">
-        <v>7227323</v>
+        <v>7227220</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1955,7 +1955,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129339070</v>
+        <v>129339073</v>
       </c>
       <c r="B15" t="n">
         <v>79070</v>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>761468</v>
+        <v>761608</v>
       </c>
       <c r="R15" t="n">
-        <v>7227315</v>
+        <v>7227323</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2052,32 +2052,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129339063</v>
+        <v>129339070</v>
       </c>
       <c r="B16" t="n">
-        <v>97633</v>
+        <v>79070</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>761450</v>
+        <v>761468</v>
       </c>
       <c r="R16" t="n">
-        <v>7227220</v>
+        <v>7227315</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2246,10 +2246,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129339062</v>
+        <v>129339068</v>
       </c>
       <c r="B18" t="n">
-        <v>57890</v>
+        <v>79070</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2257,21 +2257,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2281,10 +2281,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>761581</v>
+        <v>761608</v>
       </c>
       <c r="R18" t="n">
-        <v>7227404</v>
+        <v>7227351</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2343,10 +2343,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129339068</v>
+        <v>129339062</v>
       </c>
       <c r="B19" t="n">
-        <v>79070</v>
+        <v>57890</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2354,21 +2354,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2378,10 +2378,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>761608</v>
+        <v>761581</v>
       </c>
       <c r="R19" t="n">
-        <v>7227351</v>
+        <v>7227404</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 49216-2025 artfynd.xlsx
+++ b/artfynd/A 49216-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129339074</v>
       </c>
       <c r="B2" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129339069</v>
+        <v>129339067</v>
       </c>
       <c r="B3" t="n">
-        <v>79070</v>
+        <v>91607</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,23 +783,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -807,10 +803,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>761648</v>
+        <v>761616</v>
       </c>
       <c r="R3" t="n">
-        <v>7227085</v>
+        <v>7227248</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +865,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129339067</v>
+        <v>129339069</v>
       </c>
       <c r="B4" t="n">
-        <v>91601</v>
+        <v>79075</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,19 +876,23 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>761616</v>
+        <v>761648</v>
       </c>
       <c r="R4" t="n">
-        <v>7227248</v>
+        <v>7227085</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,10 +962,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129339065</v>
+        <v>129339077</v>
       </c>
       <c r="B5" t="n">
-        <v>80175</v>
+        <v>79075</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -973,21 +973,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -997,10 +997,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>761435</v>
+        <v>761517</v>
       </c>
       <c r="R5" t="n">
-        <v>7227306</v>
+        <v>7227429</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1041,6 +1041,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1059,10 +1060,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129339077</v>
+        <v>129339065</v>
       </c>
       <c r="B6" t="n">
-        <v>79070</v>
+        <v>80180</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1070,21 +1071,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1094,10 +1095,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>761517</v>
+        <v>761435</v>
       </c>
       <c r="R6" t="n">
-        <v>7227429</v>
+        <v>7227306</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1138,7 +1139,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1160,7 +1160,7 @@
         <v>129339072</v>
       </c>
       <c r="B7" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>129339061</v>
       </c>
       <c r="B8" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>129339076</v>
       </c>
       <c r="B9" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>129339066</v>
       </c>
       <c r="B10" t="n">
-        <v>91601</v>
+        <v>91607</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1554,27 +1554,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129339079</v>
+        <v>129339075</v>
       </c>
       <c r="B11" t="n">
-        <v>80210</v>
+        <v>79075</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>761435</v>
+        <v>761753</v>
       </c>
       <c r="R11" t="n">
-        <v>7227302</v>
+        <v>7227209</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1651,27 +1651,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129339075</v>
+        <v>129339079</v>
       </c>
       <c r="B12" t="n">
-        <v>79070</v>
+        <v>80215</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>761753</v>
+        <v>761435</v>
       </c>
       <c r="R12" t="n">
-        <v>7227209</v>
+        <v>7227302</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1751,7 +1751,7 @@
         <v>129339060</v>
       </c>
       <c r="B13" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1858,32 +1858,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129339063</v>
+        <v>129339073</v>
       </c>
       <c r="B14" t="n">
-        <v>97633</v>
+        <v>79075</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1893,10 +1893,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>761450</v>
+        <v>761608</v>
       </c>
       <c r="R14" t="n">
-        <v>7227220</v>
+        <v>7227323</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1955,10 +1955,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129339073</v>
+        <v>129339070</v>
       </c>
       <c r="B15" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>761608</v>
+        <v>761468</v>
       </c>
       <c r="R15" t="n">
-        <v>7227323</v>
+        <v>7227315</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2052,32 +2052,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129339070</v>
+        <v>129339063</v>
       </c>
       <c r="B16" t="n">
-        <v>79070</v>
+        <v>97645</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>761468</v>
+        <v>761450</v>
       </c>
       <c r="R16" t="n">
-        <v>7227315</v>
+        <v>7227220</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2152,7 +2152,7 @@
         <v>129339078</v>
       </c>
       <c r="B17" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>129339068</v>
       </c>
       <c r="B18" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>129339062</v>
       </c>
       <c r="B19" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 49216-2025 artfynd.xlsx
+++ b/artfynd/A 49216-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129339074</v>
+        <v>129339067</v>
       </c>
       <c r="B2" t="n">
-        <v>79075</v>
+        <v>91608</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,23 +686,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -710,10 +706,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>761628</v>
+        <v>761616</v>
       </c>
       <c r="R2" t="n">
-        <v>7227269</v>
+        <v>7227248</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +768,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129339067</v>
+        <v>129339074</v>
       </c>
       <c r="B3" t="n">
-        <v>91607</v>
+        <v>79076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,19 +779,23 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>761616</v>
+        <v>761628</v>
       </c>
       <c r="R3" t="n">
-        <v>7227248</v>
+        <v>7227269</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,7 +868,7 @@
         <v>129339069</v>
       </c>
       <c r="B4" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -962,10 +962,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129339077</v>
+        <v>129339065</v>
       </c>
       <c r="B5" t="n">
-        <v>79075</v>
+        <v>80181</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -973,21 +973,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -997,10 +997,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>761517</v>
+        <v>761435</v>
       </c>
       <c r="R5" t="n">
-        <v>7227429</v>
+        <v>7227306</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1041,7 +1041,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1060,10 +1059,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129339065</v>
+        <v>129339077</v>
       </c>
       <c r="B6" t="n">
-        <v>80180</v>
+        <v>79076</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1071,21 +1070,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1095,10 +1094,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>761435</v>
+        <v>761517</v>
       </c>
       <c r="R6" t="n">
-        <v>7227306</v>
+        <v>7227429</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1139,6 +1138,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1160,7 +1160,7 @@
         <v>129339072</v>
       </c>
       <c r="B7" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>129339061</v>
       </c>
       <c r="B8" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129339076</v>
+        <v>129339066</v>
       </c>
       <c r="B9" t="n">
-        <v>79075</v>
+        <v>91608</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,23 +1375,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1399,10 +1395,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>761748</v>
+        <v>761609</v>
       </c>
       <c r="R9" t="n">
-        <v>7227187</v>
+        <v>7227328</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1461,10 +1457,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129339066</v>
+        <v>129339076</v>
       </c>
       <c r="B10" t="n">
-        <v>91607</v>
+        <v>79076</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,19 +1468,23 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>761609</v>
+        <v>761748</v>
       </c>
       <c r="R10" t="n">
-        <v>7227328</v>
+        <v>7227187</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1554,10 +1554,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129339075</v>
+        <v>129339060</v>
       </c>
       <c r="B11" t="n">
-        <v>79075</v>
+        <v>57736</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1565,34 +1565,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fågelmyran, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>761753</v>
+        <v>761474</v>
       </c>
       <c r="R11" t="n">
-        <v>7227209</v>
+        <v>7227325</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1625,6 +1633,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1654,7 +1667,7 @@
         <v>129339079</v>
       </c>
       <c r="B12" t="n">
-        <v>80215</v>
+        <v>80216</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1748,10 +1761,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129339060</v>
+        <v>129339075</v>
       </c>
       <c r="B13" t="n">
-        <v>57735</v>
+        <v>79076</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1759,42 +1772,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Fågelmyran, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>761474</v>
+        <v>761753</v>
       </c>
       <c r="R13" t="n">
-        <v>7227325</v>
+        <v>7227209</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1827,11 +1832,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1861,7 +1861,7 @@
         <v>129339073</v>
       </c>
       <c r="B14" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>129339070</v>
       </c>
       <c r="B15" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>129339063</v>
       </c>
       <c r="B16" t="n">
-        <v>97645</v>
+        <v>97646</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>129339078</v>
       </c>
       <c r="B17" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>129339068</v>
       </c>
       <c r="B18" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>129339062</v>
       </c>
       <c r="B19" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 49216-2025 artfynd.xlsx
+++ b/artfynd/A 49216-2025 artfynd.xlsx
@@ -1554,53 +1554,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129339060</v>
+        <v>129339079</v>
       </c>
       <c r="B11" t="n">
-        <v>57736</v>
+        <v>80216</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fågelmyran, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>761474</v>
+        <v>761435</v>
       </c>
       <c r="R11" t="n">
-        <v>7227325</v>
+        <v>7227302</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1633,11 +1625,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1664,27 +1651,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129339079</v>
+        <v>129339075</v>
       </c>
       <c r="B12" t="n">
-        <v>80216</v>
+        <v>79076</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1699,10 +1686,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>761435</v>
+        <v>761753</v>
       </c>
       <c r="R12" t="n">
-        <v>7227302</v>
+        <v>7227209</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1761,10 +1748,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129339075</v>
+        <v>129339060</v>
       </c>
       <c r="B13" t="n">
-        <v>79076</v>
+        <v>57736</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1772,34 +1759,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Fågelmyran, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>761753</v>
+        <v>761474</v>
       </c>
       <c r="R13" t="n">
-        <v>7227209</v>
+        <v>7227325</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1832,6 +1827,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 49216-2025 artfynd.xlsx
+++ b/artfynd/A 49216-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129339067</v>
+        <v>129339074</v>
       </c>
       <c r="B2" t="n">
-        <v>91608</v>
+        <v>79081</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,19 +686,23 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -706,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>761616</v>
+        <v>761628</v>
       </c>
       <c r="R2" t="n">
-        <v>7227248</v>
+        <v>7227269</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -768,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129339074</v>
+        <v>129339069</v>
       </c>
       <c r="B3" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>761628</v>
+        <v>761648</v>
       </c>
       <c r="R3" t="n">
-        <v>7227269</v>
+        <v>7227085</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129339069</v>
+        <v>129339067</v>
       </c>
       <c r="B4" t="n">
-        <v>79076</v>
+        <v>91613</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -876,23 +880,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>761648</v>
+        <v>761616</v>
       </c>
       <c r="R4" t="n">
-        <v>7227085</v>
+        <v>7227248</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,7 +965,7 @@
         <v>129339065</v>
       </c>
       <c r="B5" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
         <v>129339077</v>
       </c>
       <c r="B6" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>129339072</v>
       </c>
       <c r="B7" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129339066</v>
+        <v>129339076</v>
       </c>
       <c r="B9" t="n">
-        <v>91608</v>
+        <v>79081</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,19 +1375,23 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1395,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>761609</v>
+        <v>761748</v>
       </c>
       <c r="R9" t="n">
-        <v>7227328</v>
+        <v>7227187</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1457,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129339076</v>
+        <v>129339066</v>
       </c>
       <c r="B10" t="n">
-        <v>79076</v>
+        <v>91613</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1468,23 +1472,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>761748</v>
+        <v>761609</v>
       </c>
       <c r="R10" t="n">
-        <v>7227187</v>
+        <v>7227328</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1557,7 +1557,7 @@
         <v>129339079</v>
       </c>
       <c r="B11" t="n">
-        <v>80216</v>
+        <v>80221</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>129339075</v>
       </c>
       <c r="B12" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>129339073</v>
       </c>
       <c r="B14" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>129339070</v>
       </c>
       <c r="B15" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>129339063</v>
       </c>
       <c r="B16" t="n">
-        <v>97646</v>
+        <v>97651</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>129339078</v>
       </c>
       <c r="B17" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>129339068</v>
       </c>
       <c r="B18" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 49216-2025 artfynd.xlsx
+++ b/artfynd/A 49216-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129339074</v>
+        <v>129339067</v>
       </c>
       <c r="B2" t="n">
-        <v>79081</v>
+        <v>91613</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,23 +686,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -710,10 +706,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>761628</v>
+        <v>761616</v>
       </c>
       <c r="R2" t="n">
-        <v>7227269</v>
+        <v>7227248</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +768,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129339069</v>
+        <v>129339074</v>
       </c>
       <c r="B3" t="n">
         <v>79081</v>
@@ -807,10 +803,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>761648</v>
+        <v>761628</v>
       </c>
       <c r="R3" t="n">
-        <v>7227085</v>
+        <v>7227269</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +865,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129339067</v>
+        <v>129339069</v>
       </c>
       <c r="B4" t="n">
-        <v>91613</v>
+        <v>79081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,19 +876,23 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>761616</v>
+        <v>761648</v>
       </c>
       <c r="R4" t="n">
-        <v>7227248</v>
+        <v>7227085</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,10 +962,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129339065</v>
+        <v>129339077</v>
       </c>
       <c r="B5" t="n">
-        <v>80186</v>
+        <v>79081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -973,21 +973,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -997,10 +997,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>761435</v>
+        <v>761517</v>
       </c>
       <c r="R5" t="n">
-        <v>7227306</v>
+        <v>7227429</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1041,6 +1041,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1059,10 +1060,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129339077</v>
+        <v>129339065</v>
       </c>
       <c r="B6" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1070,21 +1071,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1094,10 +1095,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>761517</v>
+        <v>761435</v>
       </c>
       <c r="R6" t="n">
-        <v>7227429</v>
+        <v>7227306</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1138,7 +1139,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129339076</v>
+        <v>129339066</v>
       </c>
       <c r="B9" t="n">
-        <v>79081</v>
+        <v>91613</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,23 +1375,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1399,10 +1395,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>761748</v>
+        <v>761609</v>
       </c>
       <c r="R9" t="n">
-        <v>7227187</v>
+        <v>7227328</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1461,10 +1457,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129339066</v>
+        <v>129339076</v>
       </c>
       <c r="B10" t="n">
-        <v>91613</v>
+        <v>79081</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,19 +1468,23 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>761609</v>
+        <v>761748</v>
       </c>
       <c r="R10" t="n">
-        <v>7227328</v>
+        <v>7227187</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1858,32 +1858,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129339073</v>
+        <v>129339063</v>
       </c>
       <c r="B14" t="n">
-        <v>79081</v>
+        <v>97651</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1893,10 +1893,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>761608</v>
+        <v>761450</v>
       </c>
       <c r="R14" t="n">
-        <v>7227323</v>
+        <v>7227220</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1955,7 +1955,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129339070</v>
+        <v>129339073</v>
       </c>
       <c r="B15" t="n">
         <v>79081</v>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>761468</v>
+        <v>761608</v>
       </c>
       <c r="R15" t="n">
-        <v>7227315</v>
+        <v>7227323</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2052,32 +2052,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129339063</v>
+        <v>129339070</v>
       </c>
       <c r="B16" t="n">
-        <v>97651</v>
+        <v>79081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>761450</v>
+        <v>761468</v>
       </c>
       <c r="R16" t="n">
-        <v>7227220</v>
+        <v>7227315</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2246,10 +2246,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129339068</v>
+        <v>129339062</v>
       </c>
       <c r="B18" t="n">
-        <v>79081</v>
+        <v>57896</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2257,21 +2257,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2281,10 +2281,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>761608</v>
+        <v>761581</v>
       </c>
       <c r="R18" t="n">
-        <v>7227351</v>
+        <v>7227404</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2343,10 +2343,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129339062</v>
+        <v>129339068</v>
       </c>
       <c r="B19" t="n">
-        <v>57896</v>
+        <v>79081</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2354,21 +2354,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2378,10 +2378,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>761581</v>
+        <v>761608</v>
       </c>
       <c r="R19" t="n">
-        <v>7227404</v>
+        <v>7227351</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 49216-2025 artfynd.xlsx
+++ b/artfynd/A 49216-2025 artfynd.xlsx
@@ -1858,32 +1858,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129339063</v>
+        <v>129339073</v>
       </c>
       <c r="B14" t="n">
-        <v>97651</v>
+        <v>79081</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1893,10 +1893,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>761450</v>
+        <v>761608</v>
       </c>
       <c r="R14" t="n">
-        <v>7227220</v>
+        <v>7227323</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1955,7 +1955,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129339073</v>
+        <v>129339070</v>
       </c>
       <c r="B15" t="n">
         <v>79081</v>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>761608</v>
+        <v>761468</v>
       </c>
       <c r="R15" t="n">
-        <v>7227323</v>
+        <v>7227315</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2052,32 +2052,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129339070</v>
+        <v>129339063</v>
       </c>
       <c r="B16" t="n">
-        <v>79081</v>
+        <v>97651</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>761468</v>
+        <v>761450</v>
       </c>
       <c r="R16" t="n">
-        <v>7227315</v>
+        <v>7227220</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2246,10 +2246,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129339062</v>
+        <v>129339068</v>
       </c>
       <c r="B18" t="n">
-        <v>57896</v>
+        <v>79081</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2257,21 +2257,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2281,10 +2281,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>761581</v>
+        <v>761608</v>
       </c>
       <c r="R18" t="n">
-        <v>7227404</v>
+        <v>7227351</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2343,10 +2343,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129339068</v>
+        <v>129339062</v>
       </c>
       <c r="B19" t="n">
-        <v>79081</v>
+        <v>57896</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2354,21 +2354,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2378,10 +2378,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>761608</v>
+        <v>761581</v>
       </c>
       <c r="R19" t="n">
-        <v>7227351</v>
+        <v>7227404</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
